--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.DEV\TEST_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64E9CC2-FAA2-46CD-BBB8-D9A76497CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8EA1AC-0D72-4E4B-8BA4-77E9FF888DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{5B6232BF-90C2-4A8C-9297-D00C1332E89E}"/>
   </bookViews>
@@ -1144,9 +1144,6 @@
     <t>RG80GS35153</t>
   </si>
   <si>
-    <t>251001D01</t>
-  </si>
-  <si>
     <t>RG80PA35183</t>
   </si>
   <si>
@@ -1742,6 +1739,9 @@
   </si>
   <si>
     <t>type</t>
+  </si>
+  <si>
+    <t>251014D02</t>
   </si>
 </sst>
 </file>
@@ -2198,6 +2198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2232,7 +2233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2274,7 +2275,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2295,7 +2296,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2316,7 +2317,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -2337,7 +2338,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2379,7 +2380,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2488,7 +2489,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2509,7 +2510,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2530,7 +2531,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2551,7 +2552,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2614,7 +2615,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2635,7 +2636,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -2719,7 +2720,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -2740,7 +2741,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -2824,7 +2825,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -2866,7 +2867,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -2887,7 +2888,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -2971,7 +2972,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -2992,7 +2993,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -3013,7 +3014,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -3034,7 +3035,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -3055,7 +3056,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -3076,7 +3077,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -3097,7 +3098,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -3139,7 +3140,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -3160,7 +3161,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -3181,7 +3182,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -3202,7 +3203,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -3223,7 +3224,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -3244,7 +3245,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -3286,7 +3287,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -3349,7 +3350,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -3370,7 +3371,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -3391,7 +3392,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -3433,7 +3434,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -3454,7 +3455,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -3496,7 +3497,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -3559,7 +3560,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -3580,7 +3581,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -3601,7 +3602,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>66</v>
       </c>
@@ -3622,7 +3623,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -3643,7 +3644,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>68</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -3685,7 +3686,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>70</v>
       </c>
@@ -3706,7 +3707,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -3727,7 +3728,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>72</v>
       </c>
@@ -3748,7 +3749,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>73</v>
       </c>
@@ -3769,7 +3770,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>74</v>
       </c>
@@ -3790,7 +3791,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -3811,7 +3812,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>76</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>78</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>82</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>83</v>
       </c>
@@ -3979,7 +3980,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>84</v>
       </c>
@@ -4000,7 +4001,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>86</v>
       </c>
@@ -4042,7 +4043,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -4063,7 +4064,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>88</v>
       </c>
@@ -4084,7 +4085,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>89</v>
       </c>
@@ -4105,7 +4106,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>90</v>
       </c>
@@ -4126,7 +4127,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>91</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>92</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>93</v>
       </c>
@@ -4189,7 +4190,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>94</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>95</v>
       </c>
@@ -4231,7 +4232,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>96</v>
       </c>
@@ -4252,7 +4253,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>97</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>98</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>99</v>
       </c>
@@ -4315,7 +4316,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>100</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>101</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>102</v>
       </c>
@@ -4380,7 +4381,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>103</v>
       </c>
@@ -4403,7 +4404,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>104</v>
       </c>
@@ -4426,7 +4427,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>105</v>
       </c>
@@ -4449,7 +4450,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>106</v>
       </c>
@@ -4472,7 +4473,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>107</v>
       </c>
@@ -4495,7 +4496,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>108</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>109</v>
       </c>
@@ -4541,7 +4542,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>110</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>111</v>
       </c>
@@ -4587,7 +4588,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>112</v>
       </c>
@@ -4610,7 +4611,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>113</v>
       </c>
@@ -4633,7 +4634,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>114</v>
       </c>
@@ -4656,7 +4657,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>115</v>
       </c>
@@ -4679,7 +4680,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>116</v>
       </c>
@@ -4702,7 +4703,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>117</v>
       </c>
@@ -4725,7 +4726,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>118</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>119</v>
       </c>
@@ -4771,7 +4772,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>120</v>
       </c>
@@ -4794,7 +4795,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>121</v>
       </c>
@@ -4817,7 +4818,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>122</v>
       </c>
@@ -4840,7 +4841,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>123</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>124</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>125</v>
       </c>
@@ -4909,7 +4910,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>126</v>
       </c>
@@ -4932,7 +4933,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>127</v>
       </c>
@@ -4955,7 +4956,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>128</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>129</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <v>130</v>
       </c>
@@ -5024,7 +5025,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <v>131</v>
       </c>
@@ -5047,7 +5048,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <v>132</v>
       </c>
@@ -5070,7 +5071,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <v>133</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <v>134</v>
       </c>
@@ -5112,7 +5113,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>135</v>
       </c>
@@ -5133,7 +5134,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
         <v>136</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7">
         <v>137</v>
       </c>
@@ -5175,7 +5176,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="7">
         <v>138</v>
       </c>
@@ -5196,7 +5197,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7">
         <v>139</v>
       </c>
@@ -5217,7 +5218,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="7">
         <v>140</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7">
         <v>141</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="7">
         <v>142</v>
       </c>
@@ -5280,7 +5281,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="7">
         <v>143</v>
       </c>
@@ -5301,7 +5302,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="7">
         <v>144</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="7">
         <v>145</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="7">
         <v>146</v>
       </c>
@@ -5364,7 +5365,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="7">
         <v>147</v>
       </c>
@@ -5385,7 +5386,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="7">
         <v>148</v>
       </c>
@@ -5406,7 +5407,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="7">
         <v>149</v>
       </c>
@@ -5427,7 +5428,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="7">
         <v>150</v>
       </c>
@@ -5448,7 +5449,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="7">
         <v>151</v>
       </c>
@@ -5469,7 +5470,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="7">
         <v>152</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="7">
         <v>153</v>
       </c>
@@ -5511,7 +5512,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="7">
         <v>154</v>
       </c>
@@ -5532,7 +5533,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="7">
         <v>155</v>
       </c>
@@ -5553,7 +5554,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
         <v>156</v>
       </c>
@@ -5574,7 +5575,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>157</v>
       </c>
@@ -5595,7 +5596,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
         <v>158</v>
       </c>
@@ -5616,7 +5617,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
         <v>159</v>
       </c>
@@ -5639,7 +5640,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
         <v>160</v>
       </c>
@@ -5662,7 +5663,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>161</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
         <v>162</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
         <v>163</v>
       </c>
@@ -5731,7 +5732,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="7">
         <v>164</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7">
         <v>165</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
         <v>166</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
         <v>167</v>
       </c>
@@ -5823,7 +5824,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
         <v>168</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
         <v>169</v>
       </c>
@@ -5869,7 +5870,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
         <v>170</v>
       </c>
@@ -5892,7 +5893,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
         <v>172</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
         <v>173</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
         <v>174</v>
       </c>
@@ -5955,7 +5956,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7">
         <v>175</v>
       </c>
@@ -5976,7 +5977,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7">
         <v>176</v>
       </c>
@@ -5997,7 +5998,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7">
         <v>177</v>
       </c>
@@ -6018,7 +6019,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="7">
         <v>178</v>
       </c>
@@ -6039,7 +6040,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7">
         <v>179</v>
       </c>
@@ -6060,7 +6061,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7">
         <v>180</v>
       </c>
@@ -6081,7 +6082,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7">
         <v>181</v>
       </c>
@@ -6102,7 +6103,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7">
         <v>182</v>
       </c>
@@ -6123,7 +6124,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7">
         <v>183</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7">
         <v>184</v>
       </c>
@@ -6165,7 +6166,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7">
         <v>185</v>
       </c>
@@ -6186,7 +6187,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7">
         <v>186</v>
       </c>
@@ -6207,7 +6208,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
         <v>187</v>
       </c>
@@ -6228,7 +6229,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
         <v>188</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
         <v>189</v>
       </c>
@@ -6270,7 +6271,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
         <v>190</v>
       </c>
@@ -6291,7 +6292,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
         <v>191</v>
       </c>
@@ -6312,7 +6313,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
         <v>192</v>
       </c>
@@ -6333,7 +6334,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7">
         <v>193</v>
       </c>
@@ -6354,7 +6355,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7">
         <v>194</v>
       </c>
@@ -6375,7 +6376,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7">
         <v>195</v>
       </c>
@@ -6396,7 +6397,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7">
         <v>196</v>
       </c>
@@ -6417,7 +6418,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7">
         <v>197</v>
       </c>
@@ -6440,7 +6441,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7">
         <v>198</v>
       </c>
@@ -6461,7 +6462,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7">
         <v>199</v>
       </c>
@@ -6484,7 +6485,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <v>200</v>
       </c>
@@ -6507,7 +6508,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7">
         <v>201</v>
       </c>
@@ -6530,7 +6531,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7">
         <v>202</v>
       </c>
@@ -6553,7 +6554,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7">
         <v>203</v>
       </c>
@@ -6576,7 +6577,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7">
         <v>204</v>
       </c>
@@ -6599,7 +6600,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7">
         <v>205</v>
       </c>
@@ -6622,7 +6623,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7">
         <v>206</v>
       </c>
@@ -6645,7 +6646,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7">
         <v>171</v>
       </c>
@@ -6668,7 +6669,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7">
         <v>207</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7">
         <v>208</v>
       </c>
@@ -6710,7 +6711,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="7">
         <v>209</v>
       </c>
@@ -6731,7 +6732,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7">
         <v>210</v>
       </c>
@@ -6752,7 +6753,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7">
         <v>211</v>
       </c>
@@ -6773,7 +6774,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7">
         <v>212</v>
       </c>
@@ -6794,7 +6795,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7">
         <v>213</v>
       </c>
@@ -6815,7 +6816,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7">
         <v>214</v>
       </c>
@@ -6836,7 +6837,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7">
         <v>215</v>
       </c>
@@ -6859,7 +6860,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7">
         <v>216</v>
       </c>
@@ -6882,7 +6883,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="7">
         <v>217</v>
       </c>
@@ -6903,7 +6904,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="7">
         <v>218</v>
       </c>
@@ -6924,7 +6925,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7">
         <v>219</v>
       </c>
@@ -6945,7 +6946,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7">
         <v>220</v>
       </c>
@@ -6966,7 +6967,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="7">
         <v>221</v>
       </c>
@@ -6987,7 +6988,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="7">
         <v>222</v>
       </c>
@@ -7008,7 +7009,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="7">
         <v>223</v>
       </c>
@@ -7029,7 +7030,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="7">
         <v>224</v>
       </c>
@@ -7050,7 +7051,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="7">
         <v>225</v>
       </c>
@@ -7071,7 +7072,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="7">
         <v>226</v>
       </c>
@@ -7092,7 +7093,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="7">
         <v>227</v>
       </c>
@@ -7113,7 +7114,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="7">
         <v>228</v>
       </c>
@@ -7136,7 +7137,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7">
         <v>229</v>
       </c>
@@ -7159,7 +7160,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="7">
         <v>230</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="7">
         <v>231</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="7">
         <v>232</v>
       </c>
@@ -7228,7 +7229,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="7">
         <v>233</v>
       </c>
@@ -7251,7 +7252,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="7">
         <v>234</v>
       </c>
@@ -7274,7 +7275,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="7">
         <v>235</v>
       </c>
@@ -7297,7 +7298,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7">
         <v>236</v>
       </c>
@@ -7320,7 +7321,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="7">
         <v>237</v>
       </c>
@@ -7343,7 +7344,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="7">
         <v>238</v>
       </c>
@@ -7366,7 +7367,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="7">
         <v>239</v>
       </c>
@@ -7389,7 +7390,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="7">
         <v>240</v>
       </c>
@@ -7412,7 +7413,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="7">
         <v>241</v>
       </c>
@@ -7435,7 +7436,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="7">
         <v>242</v>
       </c>
@@ -7458,7 +7459,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="7">
         <v>243</v>
       </c>
@@ -7481,7 +7482,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="7">
         <v>244</v>
       </c>
@@ -7504,7 +7505,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="7">
         <v>245</v>
       </c>
@@ -7527,7 +7528,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="7">
         <v>246</v>
       </c>
@@ -7550,7 +7551,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="7">
         <v>247</v>
       </c>
@@ -7573,7 +7574,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="7">
         <v>248</v>
       </c>
@@ -7594,7 +7595,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="7">
         <v>249</v>
       </c>
@@ -7615,7 +7616,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="7">
         <v>250</v>
       </c>
@@ -7636,7 +7637,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7">
         <v>251</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="7">
         <v>252</v>
       </c>
@@ -7678,7 +7679,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="7">
         <v>253</v>
       </c>
@@ -7699,7 +7700,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="7">
         <v>254</v>
       </c>
@@ -7720,7 +7721,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="7">
         <v>255</v>
       </c>
@@ -7741,7 +7742,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="7">
         <v>256</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="7">
         <v>257</v>
       </c>
@@ -7785,7 +7786,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="7">
         <v>258</v>
       </c>
@@ -7808,7 +7809,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="7">
         <v>259</v>
       </c>
@@ -7829,7 +7830,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="7">
         <v>260</v>
       </c>
@@ -7850,7 +7851,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7">
         <v>261</v>
       </c>
@@ -7871,7 +7872,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7">
         <v>262</v>
       </c>
@@ -7892,7 +7893,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7">
         <v>263</v>
       </c>
@@ -7913,7 +7914,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7">
         <v>264</v>
       </c>
@@ -7934,7 +7935,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="7">
         <v>265</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="7">
         <v>266</v>
       </c>
@@ -7976,7 +7977,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="7">
         <v>267</v>
       </c>
@@ -7997,7 +7998,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="7">
         <v>268</v>
       </c>
@@ -8020,7 +8021,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="7">
         <v>269</v>
       </c>
@@ -8043,7 +8044,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="7">
         <v>270</v>
       </c>
@@ -8064,7 +8065,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="7">
         <v>271</v>
       </c>
@@ -8085,7 +8086,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="7">
         <v>272</v>
       </c>
@@ -8108,7 +8109,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="7">
         <v>273</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="7">
         <v>274</v>
       </c>
@@ -8154,7 +8155,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="7">
         <v>275</v>
       </c>
@@ -8175,7 +8176,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="7">
         <v>276</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="7">
         <v>277</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="7">
         <v>278</v>
       </c>
@@ -8238,7 +8239,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="7">
         <v>279</v>
       </c>
@@ -8259,7 +8260,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="7">
         <v>280</v>
       </c>
@@ -8280,7 +8281,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="7">
         <v>281</v>
       </c>
@@ -8301,7 +8302,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="7">
         <v>282</v>
       </c>
@@ -8322,7 +8323,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="7">
         <v>283</v>
       </c>
@@ -8345,7 +8346,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="7">
         <v>284</v>
       </c>
@@ -8368,7 +8369,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7">
         <v>285</v>
       </c>
@@ -8391,7 +8392,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="7">
         <v>286</v>
       </c>
@@ -8414,7 +8415,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="7">
         <v>287</v>
       </c>
@@ -8437,7 +8438,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="7">
         <v>288</v>
       </c>
@@ -8460,7 +8461,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="7">
         <v>289</v>
       </c>
@@ -8483,7 +8484,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="7">
         <v>290</v>
       </c>
@@ -8506,7 +8507,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="7">
         <v>291</v>
       </c>
@@ -8527,7 +8528,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="7">
         <v>292</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="7">
         <v>293</v>
       </c>
@@ -8571,7 +8572,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="7">
         <v>294</v>
       </c>
@@ -8594,7 +8595,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="7">
         <v>295</v>
       </c>
@@ -8617,7 +8618,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7">
         <v>296</v>
       </c>
@@ -8640,7 +8641,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="7">
         <v>297</v>
       </c>
@@ -8663,7 +8664,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="7">
         <v>298</v>
       </c>
@@ -8681,10 +8682,10 @@
       </c>
       <c r="F299" s="8"/>
       <c r="G299" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="7">
         <v>299</v>
       </c>
@@ -8702,10 +8703,10 @@
       </c>
       <c r="F300" s="8"/>
       <c r="G300" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="7">
         <v>300</v>
       </c>
@@ -8723,10 +8724,10 @@
       </c>
       <c r="F301" s="8"/>
       <c r="G301" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="7">
         <v>301</v>
       </c>
@@ -8744,10 +8745,10 @@
       </c>
       <c r="F302" s="8"/>
       <c r="G302" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="7">
         <v>302</v>
       </c>
@@ -8765,10 +8766,10 @@
       </c>
       <c r="F303" s="8"/>
       <c r="G303" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="7">
         <v>303</v>
       </c>
@@ -8786,10 +8787,10 @@
       </c>
       <c r="F304" s="8"/>
       <c r="G304" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="7">
         <v>304</v>
       </c>
@@ -8807,10 +8808,10 @@
       </c>
       <c r="F305" s="8"/>
       <c r="G305" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="7">
         <v>305</v>
       </c>
@@ -8828,10 +8829,10 @@
       </c>
       <c r="F306" s="8"/>
       <c r="G306" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="7">
         <v>306</v>
       </c>
@@ -8849,10 +8850,10 @@
       </c>
       <c r="F307" s="8"/>
       <c r="G307" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="7">
         <v>307</v>
       </c>
@@ -8870,10 +8871,10 @@
       </c>
       <c r="F308" s="8"/>
       <c r="G308" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="7">
         <v>308</v>
       </c>
@@ -8891,10 +8892,10 @@
       </c>
       <c r="F309" s="8"/>
       <c r="G309" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="7">
         <v>309</v>
       </c>
@@ -8912,10 +8913,10 @@
       </c>
       <c r="F310" s="8"/>
       <c r="G310" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="7">
         <v>310</v>
       </c>
@@ -8933,10 +8934,10 @@
       </c>
       <c r="F311" s="8"/>
       <c r="G311" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="7">
         <v>311</v>
       </c>
@@ -8954,10 +8955,10 @@
       </c>
       <c r="F312" s="8"/>
       <c r="G312" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="7">
         <v>312</v>
       </c>
@@ -8975,10 +8976,10 @@
       </c>
       <c r="F313" s="8"/>
       <c r="G313" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="7">
         <v>313</v>
       </c>
@@ -8996,10 +8997,10 @@
       </c>
       <c r="F314" s="8"/>
       <c r="G314" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="7">
         <v>314</v>
       </c>
@@ -9017,10 +9018,10 @@
       </c>
       <c r="F315" s="8"/>
       <c r="G315" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="7">
         <v>315</v>
       </c>
@@ -9038,10 +9039,10 @@
       </c>
       <c r="F316" s="8"/>
       <c r="G316" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="7">
         <v>316</v>
       </c>
@@ -9059,10 +9060,10 @@
       </c>
       <c r="F317" s="8"/>
       <c r="G317" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="7">
         <v>317</v>
       </c>
@@ -9080,10 +9081,10 @@
       </c>
       <c r="F318" s="8"/>
       <c r="G318" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="7">
         <v>318</v>
       </c>
@@ -9101,10 +9102,10 @@
       </c>
       <c r="F319" s="8"/>
       <c r="G319" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="7">
         <v>319</v>
       </c>
@@ -9122,10 +9123,10 @@
       </c>
       <c r="F320" s="8"/>
       <c r="G320" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="7">
         <v>320</v>
       </c>
@@ -9143,10 +9144,10 @@
       </c>
       <c r="F321" s="8"/>
       <c r="G321" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="7">
         <v>321</v>
       </c>
@@ -9164,10 +9165,10 @@
       </c>
       <c r="F322" s="8"/>
       <c r="G322" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="7">
         <v>322</v>
       </c>
@@ -9185,10 +9186,10 @@
       </c>
       <c r="F323" s="8"/>
       <c r="G323" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="7">
         <v>323</v>
       </c>
@@ -9206,10 +9207,10 @@
       </c>
       <c r="F324" s="8"/>
       <c r="G324" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="7">
         <v>324</v>
       </c>
@@ -9227,10 +9228,10 @@
       </c>
       <c r="F325" s="8"/>
       <c r="G325" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="7">
         <v>325</v>
       </c>
@@ -9248,10 +9249,10 @@
       </c>
       <c r="F326" s="8"/>
       <c r="G326" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="7">
         <v>326</v>
       </c>
@@ -9269,10 +9270,10 @@
       </c>
       <c r="F327" s="8"/>
       <c r="G327" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="7">
         <v>327</v>
       </c>
@@ -9290,10 +9291,10 @@
       </c>
       <c r="F328" s="8"/>
       <c r="G328" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="7">
         <v>328</v>
       </c>
@@ -9311,10 +9312,10 @@
       </c>
       <c r="F329" s="8"/>
       <c r="G329" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="7">
         <v>329</v>
       </c>
@@ -9325,17 +9326,17 @@
         <v>350</v>
       </c>
       <c r="D330" s="7">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="E330" s="8">
         <v>45992</v>
       </c>
       <c r="F330" s="8"/>
       <c r="G330" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="7">
         <v>330</v>
       </c>
@@ -9353,10 +9354,10 @@
       </c>
       <c r="F331" s="8"/>
       <c r="G331" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="7">
         <v>331</v>
       </c>
@@ -9374,7 +9375,7 @@
       </c>
       <c r="F332" s="8"/>
       <c r="G332" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
@@ -9395,10 +9396,10 @@
       </c>
       <c r="F333" s="8"/>
       <c r="G333" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="7">
         <v>333</v>
       </c>
@@ -9416,10 +9417,10 @@
       </c>
       <c r="F334" s="8"/>
       <c r="G334" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="7">
         <v>334</v>
       </c>
@@ -9437,53 +9438,62 @@
       </c>
       <c r="F335" s="8"/>
       <c r="G335" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D336" s="7">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E336" s="8">
-        <v>46008</v>
+        <v>46021</v>
       </c>
       <c r="F336" s="8"/>
       <c r="G336" s="7" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A337" s="7">
-        <v>336</v>
-      </c>
-      <c r="B337" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C337" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D337" s="7">
-        <v>544</v>
-      </c>
-      <c r="E337" s="8">
-        <v>46021</v>
-      </c>
-      <c r="F337" s="8"/>
-      <c r="G337" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>337</v>
+      </c>
+      <c r="B337" t="s">
+        <v>356</v>
+      </c>
+      <c r="C337" t="s">
+        <v>566</v>
+      </c>
+      <c r="D337">
+        <v>1000</v>
+      </c>
+      <c r="E337" s="6">
+        <v>45992</v>
+      </c>
+      <c r="G337" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F337" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}"/>
+  <autoFilter ref="A1:F337" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="RG80GS35153"/>
+        <filter val="RG80GS35153Y"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B6:B13">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -9495,9 +9505,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -9518,1014 +9525,1014 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C1" t="s">
         <v>565</v>
-      </c>
-      <c r="B1" t="s">
-        <v>564</v>
-      </c>
-      <c r="C1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B2" t="s">
         <v>315</v>
       </c>
       <c r="C2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B3" t="s">
         <v>329</v>
       </c>
       <c r="C3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B4" t="s">
         <v>372</v>
       </c>
-      <c r="B4" t="s">
-        <v>373</v>
-      </c>
       <c r="C4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" t="s">
         <v>374</v>
       </c>
-      <c r="B5" t="s">
-        <v>375</v>
-      </c>
       <c r="C5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B6" t="s">
         <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" t="s">
         <v>377</v>
       </c>
-      <c r="B7" t="s">
-        <v>378</v>
-      </c>
       <c r="C7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
         <v>356</v>
       </c>
       <c r="C8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B9" t="s">
         <v>357</v>
       </c>
       <c r="C9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B10" t="s">
         <v>322</v>
       </c>
       <c r="C10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B11" t="s">
         <v>359</v>
       </c>
       <c r="C11" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B12" t="s">
         <v>320</v>
       </c>
       <c r="C12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" t="s">
         <v>384</v>
       </c>
-      <c r="B13" t="s">
-        <v>385</v>
-      </c>
       <c r="C13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s">
         <v>335</v>
       </c>
       <c r="C14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B15" t="s">
         <v>387</v>
       </c>
-      <c r="B15" t="s">
-        <v>388</v>
-      </c>
       <c r="C15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>388</v>
+      </c>
+      <c r="B16" t="s">
         <v>389</v>
       </c>
-      <c r="B16" t="s">
-        <v>390</v>
-      </c>
       <c r="C16" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B17" t="s">
         <v>336</v>
       </c>
       <c r="C17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" t="s">
         <v>392</v>
       </c>
-      <c r="B18" t="s">
-        <v>393</v>
-      </c>
       <c r="C18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B19" t="s">
         <v>394</v>
       </c>
-      <c r="B19" t="s">
-        <v>395</v>
-      </c>
       <c r="C19" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B20" t="s">
         <v>318</v>
       </c>
       <c r="C20" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B21" t="s">
         <v>361</v>
       </c>
       <c r="C21" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B22" t="s">
         <v>366</v>
       </c>
       <c r="C22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B23" t="s">
         <v>324</v>
       </c>
       <c r="C23" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B24" t="s">
         <v>331</v>
       </c>
       <c r="C24" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B25" t="s">
         <v>316</v>
       </c>
       <c r="C25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B26" t="s">
         <v>319</v>
       </c>
       <c r="C26" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>401</v>
+      </c>
+      <c r="B27" t="s">
         <v>402</v>
       </c>
-      <c r="B27" t="s">
-        <v>403</v>
-      </c>
       <c r="C27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>403</v>
+      </c>
+      <c r="B28" t="s">
         <v>404</v>
       </c>
-      <c r="B28" t="s">
-        <v>405</v>
-      </c>
       <c r="C28" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>405</v>
+      </c>
+      <c r="B29" t="s">
         <v>406</v>
       </c>
-      <c r="B29" t="s">
-        <v>407</v>
-      </c>
       <c r="C29" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>407</v>
+      </c>
+      <c r="B30" t="s">
         <v>408</v>
       </c>
-      <c r="B30" t="s">
-        <v>409</v>
-      </c>
       <c r="C30" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>409</v>
+      </c>
+      <c r="B31" t="s">
         <v>410</v>
       </c>
-      <c r="B31" t="s">
-        <v>411</v>
-      </c>
       <c r="C31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B32" t="s">
         <v>412</v>
       </c>
-      <c r="B32" t="s">
-        <v>413</v>
-      </c>
       <c r="C32" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>413</v>
+      </c>
+      <c r="B33" t="s">
         <v>414</v>
       </c>
-      <c r="B33" t="s">
-        <v>415</v>
-      </c>
       <c r="C33" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>415</v>
+      </c>
+      <c r="B34" t="s">
         <v>416</v>
       </c>
-      <c r="B34" t="s">
-        <v>417</v>
-      </c>
       <c r="C34" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B36" t="s">
         <v>363</v>
       </c>
       <c r="C36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>419</v>
+      </c>
+      <c r="B37" t="s">
         <v>420</v>
       </c>
-      <c r="B37" t="s">
-        <v>421</v>
-      </c>
       <c r="C37" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>421</v>
+      </c>
+      <c r="B38" t="s">
         <v>422</v>
       </c>
-      <c r="B38" t="s">
-        <v>423</v>
-      </c>
       <c r="C38" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B39" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B40" t="s">
         <v>365</v>
       </c>
       <c r="C40" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B41" t="s">
         <v>327</v>
       </c>
       <c r="C41" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s">
         <v>326</v>
       </c>
       <c r="C42" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s">
         <v>333</v>
       </c>
       <c r="C43" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>428</v>
+      </c>
+      <c r="B44" t="s">
         <v>429</v>
       </c>
-      <c r="B44" t="s">
-        <v>430</v>
-      </c>
       <c r="C44" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>430</v>
+      </c>
+      <c r="B45" t="s">
         <v>431</v>
       </c>
-      <c r="B45" t="s">
-        <v>432</v>
-      </c>
       <c r="C45" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s">
         <v>339</v>
       </c>
       <c r="C46" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>433</v>
+      </c>
+      <c r="B47" t="s">
         <v>434</v>
       </c>
-      <c r="B47" t="s">
-        <v>435</v>
-      </c>
       <c r="C47" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s">
         <v>341</v>
       </c>
       <c r="C48" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>436</v>
+      </c>
+      <c r="B49" t="s">
         <v>437</v>
       </c>
-      <c r="B49" t="s">
-        <v>438</v>
-      </c>
       <c r="C49" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s">
         <v>342</v>
       </c>
       <c r="C50" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s">
         <v>343</v>
       </c>
       <c r="C51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" t="s">
         <v>441</v>
       </c>
-      <c r="B52" t="s">
-        <v>442</v>
-      </c>
       <c r="C52" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>442</v>
+      </c>
+      <c r="B53" t="s">
         <v>443</v>
       </c>
-      <c r="B53" t="s">
-        <v>444</v>
-      </c>
       <c r="C53" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s">
         <v>313</v>
       </c>
       <c r="C54" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s">
         <v>344</v>
       </c>
       <c r="C55" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s">
         <v>346</v>
       </c>
       <c r="C56" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s">
         <v>348</v>
       </c>
       <c r="C57" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>448</v>
+      </c>
+      <c r="B58" t="s">
         <v>449</v>
       </c>
-      <c r="B58" t="s">
-        <v>450</v>
-      </c>
       <c r="C58" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>450</v>
+      </c>
+      <c r="B59" t="s">
         <v>451</v>
       </c>
-      <c r="B59" t="s">
-        <v>452</v>
-      </c>
       <c r="C59" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>452</v>
+      </c>
+      <c r="B60" t="s">
         <v>453</v>
       </c>
-      <c r="B60" t="s">
-        <v>454</v>
-      </c>
       <c r="C60" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>454</v>
+      </c>
+      <c r="B61" t="s">
         <v>455</v>
       </c>
-      <c r="B61" t="s">
-        <v>456</v>
-      </c>
       <c r="C61" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s">
         <v>349</v>
       </c>
       <c r="C62" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>457</v>
+      </c>
+      <c r="B63" t="s">
         <v>458</v>
       </c>
-      <c r="B63" t="s">
-        <v>459</v>
-      </c>
       <c r="C63" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>459</v>
+      </c>
+      <c r="B64" t="s">
         <v>460</v>
       </c>
-      <c r="B64" t="s">
-        <v>461</v>
-      </c>
       <c r="C64" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>461</v>
+      </c>
+      <c r="B65" t="s">
         <v>462</v>
       </c>
-      <c r="B65" t="s">
-        <v>463</v>
-      </c>
       <c r="C65" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>463</v>
+      </c>
+      <c r="B66" t="s">
         <v>464</v>
       </c>
-      <c r="B66" t="s">
-        <v>465</v>
-      </c>
       <c r="C66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>465</v>
+      </c>
+      <c r="B67" t="s">
         <v>466</v>
       </c>
-      <c r="B67" t="s">
-        <v>467</v>
-      </c>
       <c r="C67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>467</v>
+      </c>
+      <c r="B68" t="s">
         <v>468</v>
       </c>
-      <c r="B68" t="s">
-        <v>469</v>
-      </c>
       <c r="C68" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s">
         <v>351</v>
       </c>
       <c r="C69" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>470</v>
+      </c>
+      <c r="B70" t="s">
         <v>471</v>
       </c>
-      <c r="B70" t="s">
-        <v>472</v>
-      </c>
       <c r="C70" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B71" t="s">
         <v>353</v>
       </c>
       <c r="C71" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B72" t="s">
         <v>354</v>
       </c>
       <c r="C72" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>474</v>
+      </c>
+      <c r="B73" t="s">
         <v>475</v>
       </c>
-      <c r="B73" t="s">
-        <v>476</v>
-      </c>
       <c r="C73" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>476</v>
+      </c>
+      <c r="B74" t="s">
         <v>477</v>
       </c>
-      <c r="B74" t="s">
-        <v>478</v>
-      </c>
       <c r="C74" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>478</v>
+      </c>
+      <c r="B75" t="s">
         <v>479</v>
       </c>
-      <c r="B75" t="s">
-        <v>480</v>
-      </c>
       <c r="C75" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>480</v>
+      </c>
+      <c r="B76" t="s">
         <v>481</v>
       </c>
-      <c r="B76" t="s">
-        <v>482</v>
-      </c>
       <c r="C76" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>482</v>
+      </c>
+      <c r="B77" t="s">
         <v>483</v>
       </c>
-      <c r="B77" t="s">
-        <v>484</v>
-      </c>
       <c r="C77" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>484</v>
+      </c>
+      <c r="B78" t="s">
         <v>485</v>
       </c>
-      <c r="B78" t="s">
-        <v>486</v>
-      </c>
       <c r="C78" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>486</v>
+      </c>
+      <c r="B79" t="s">
         <v>487</v>
       </c>
-      <c r="B79" t="s">
-        <v>488</v>
-      </c>
       <c r="C79" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>488</v>
+      </c>
+      <c r="B80" t="s">
         <v>489</v>
       </c>
-      <c r="B80" t="s">
-        <v>490</v>
-      </c>
       <c r="C80" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>490</v>
+      </c>
+      <c r="B81" t="s">
         <v>491</v>
       </c>
-      <c r="B81" t="s">
-        <v>492</v>
-      </c>
       <c r="C81" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>492</v>
+      </c>
+      <c r="B82" t="s">
         <v>493</v>
       </c>
-      <c r="B82" t="s">
-        <v>494</v>
-      </c>
       <c r="C82" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>494</v>
+      </c>
+      <c r="B83" t="s">
         <v>495</v>
       </c>
-      <c r="B83" t="s">
-        <v>496</v>
-      </c>
       <c r="C83" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>496</v>
+      </c>
+      <c r="B84" t="s">
         <v>497</v>
       </c>
-      <c r="B84" t="s">
-        <v>498</v>
-      </c>
       <c r="C84" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>498</v>
+      </c>
+      <c r="B85" t="s">
         <v>499</v>
       </c>
-      <c r="B85" t="s">
-        <v>500</v>
-      </c>
       <c r="C85" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>500</v>
+      </c>
+      <c r="B86" t="s">
         <v>501</v>
       </c>
-      <c r="B86" t="s">
-        <v>502</v>
-      </c>
       <c r="C86" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B87" t="s">
         <v>355</v>
       </c>
       <c r="C87" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>503</v>
+      </c>
+      <c r="B88" t="s">
         <v>504</v>
       </c>
-      <c r="B88" t="s">
-        <v>505</v>
-      </c>
       <c r="C88" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>505</v>
+      </c>
+      <c r="B89" t="s">
         <v>506</v>
       </c>
-      <c r="B89" t="s">
-        <v>507</v>
-      </c>
       <c r="C89" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>507</v>
+      </c>
+      <c r="B90" t="s">
         <v>508</v>
       </c>
-      <c r="B90" t="s">
-        <v>509</v>
-      </c>
       <c r="C90" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>509</v>
+      </c>
+      <c r="B91" t="s">
         <v>510</v>
       </c>
-      <c r="B91" t="s">
-        <v>511</v>
-      </c>
       <c r="C91" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>511</v>
+      </c>
+      <c r="B92" t="s">
         <v>512</v>
       </c>
-      <c r="B92" t="s">
-        <v>513</v>
-      </c>
       <c r="C92" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10536,7 +10543,7 @@
         <v>301</v>
       </c>
       <c r="C93" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10547,29 +10554,29 @@
         <v>302</v>
       </c>
       <c r="C94" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B95" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C95" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B96" t="s">
         <v>298</v>
       </c>
       <c r="C96" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10577,21 +10584,21 @@
         <v>337</v>
       </c>
       <c r="B97" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C97" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B98" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C98" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10602,7 +10609,7 @@
         <v>287</v>
       </c>
       <c r="C99" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10613,7 +10620,7 @@
         <v>288</v>
       </c>
       <c r="C100" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10621,10 +10628,10 @@
         <v>322</v>
       </c>
       <c r="B101" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C101" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10635,7 +10642,7 @@
         <v>289</v>
       </c>
       <c r="C102" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10643,21 +10650,21 @@
         <v>320</v>
       </c>
       <c r="B103" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C103" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B104" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C104" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10668,29 +10675,29 @@
         <v>300</v>
       </c>
       <c r="C105" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B106" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C106" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B107" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C107" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10698,32 +10705,32 @@
         <v>336</v>
       </c>
       <c r="B108" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C108" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B109" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C109" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B110" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C110" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10731,13 +10738,13 @@
         <v>318</v>
       </c>
       <c r="B111" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C111" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>361</v>
       </c>
@@ -10745,10 +10752,10 @@
         <v>290</v>
       </c>
       <c r="C112" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>366</v>
       </c>
@@ -10756,7 +10763,7 @@
         <v>285</v>
       </c>
       <c r="C113" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10767,7 +10774,7 @@
         <v>297</v>
       </c>
       <c r="C114" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10778,7 +10785,7 @@
         <v>303</v>
       </c>
       <c r="C115" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10786,10 +10793,10 @@
         <v>316</v>
       </c>
       <c r="B116" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C116" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10800,106 +10807,106 @@
         <v>296</v>
       </c>
       <c r="C117" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B118" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C118" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B119" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C119" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B120" t="s">
         <v>299</v>
       </c>
       <c r="C120" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B121" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C121" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B122" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B123" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C123" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B124" t="s">
         <v>293</v>
       </c>
       <c r="C124" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B125" t="s">
         <v>292</v>
       </c>
       <c r="C125" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B126" t="s">
         <v>286</v>
       </c>
       <c r="C126" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10910,40 +10917,40 @@
         <v>291</v>
       </c>
       <c r="C127" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B128" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C128" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B129" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C129" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B130" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C130" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10954,7 +10961,7 @@
         <v>294</v>
       </c>
       <c r="C131" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10962,10 +10969,10 @@
         <v>327</v>
       </c>
       <c r="B132" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C132" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10976,7 +10983,7 @@
         <v>304</v>
       </c>
       <c r="C133" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -10987,29 +10994,29 @@
         <v>295</v>
       </c>
       <c r="C134" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B135" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C135" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B136" t="s">
         <v>309</v>
       </c>
       <c r="C136" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11017,21 +11024,21 @@
         <v>339</v>
       </c>
       <c r="B137" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C137" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B138" t="s">
         <v>311</v>
       </c>
       <c r="C138" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11042,18 +11049,18 @@
         <v>308</v>
       </c>
       <c r="C139" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B140" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C140" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11064,7 +11071,7 @@
         <v>305</v>
       </c>
       <c r="C141" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11072,32 +11079,32 @@
         <v>343</v>
       </c>
       <c r="B142" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C142" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B143" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C143" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B144" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C144" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11105,10 +11112,10 @@
         <v>313</v>
       </c>
       <c r="B145" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C145" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11116,10 +11123,10 @@
         <v>344</v>
       </c>
       <c r="B146" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C146" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11130,7 +11137,7 @@
         <v>306</v>
       </c>
       <c r="C147" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11138,54 +11145,54 @@
         <v>348</v>
       </c>
       <c r="B148" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C148" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B149" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C149" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B150" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C150" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B151" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C151" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B152" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C152" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11193,76 +11200,76 @@
         <v>349</v>
       </c>
       <c r="B153" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C153" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B154" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C154" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B155" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C155" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B156" t="s">
         <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B157" t="s">
         <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B158" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C158" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B159" t="s">
         <v>301</v>
       </c>
       <c r="C159" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11273,18 +11280,18 @@
         <v>298</v>
       </c>
       <c r="C160" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B161" t="s">
         <v>308</v>
       </c>
       <c r="C161" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11295,7 +11302,7 @@
         <v>307</v>
       </c>
       <c r="C162" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11306,161 +11313,161 @@
         <v>307</v>
       </c>
       <c r="C163" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B164" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C164" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B165" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C165" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B166" t="s">
         <v>300</v>
       </c>
       <c r="C166" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B167" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C167" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B168" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C168" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B169" t="s">
         <v>290</v>
       </c>
       <c r="C169" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B170" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C170" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B171" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C171" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B172" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C172" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B173" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C173" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B174" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C174" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B175" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C175" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B176" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C176" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B177" t="s">
         <v>310</v>
       </c>
       <c r="C177" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
@@ -11468,77 +11475,77 @@
         <v>355</v>
       </c>
       <c r="B178" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C178" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B179" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C179" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B180" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C180" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B181" t="s">
         <v>294</v>
       </c>
       <c r="C181" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B182" t="s">
         <v>295</v>
       </c>
       <c r="C182" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B183" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C183" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D183" xr:uid="{3AB63DC0-C6F4-49B3-A9D9-717587D0D359}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="RG75GS35153V"/>
+        <filter val="RG80GS35153Y"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.DEV\TEST_python\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJ\testpython\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8EA1AC-0D72-4E4B-8BA4-77E9FF888DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883F0F30-5F20-4C15-86B1-1A884A8385AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{5B6232BF-90C2-4A8C-9297-D00C1332E89E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B6232BF-90C2-4A8C-9297-D00C1332E89E}"/>
   </bookViews>
   <sheets>
     <sheet name="inventory" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BOM!$A$1:$D$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inventory!$A$1:$F$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inventory!$A$1:$K$333</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="566">
   <si>
     <t>stt</t>
   </si>
@@ -1739,9 +1739,6 @@
   </si>
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>251014D02</t>
   </si>
 </sst>
 </file>
@@ -2199,7 +2196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G337"/>
+  <dimension ref="A1:K333"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
@@ -2208,9 +2205,10 @@
     <col min="5" max="5" width="15" style="6" customWidth="1"/>
     <col min="6" max="6" width="14.140625" style="6" customWidth="1"/>
     <col min="7" max="7" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2233,7 +2231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2253,8 +2251,12 @@
       <c r="G2" s="7" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <f>SUM(D2:D333)</f>
+        <v>2616605</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2275,7 +2277,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2296,7 +2298,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2316,8 +2318,12 @@
       <c r="G5" s="7" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K5" t="e">
+        <f>K2-#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -2338,7 +2344,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2359,7 +2365,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2380,7 +2386,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2401,7 +2407,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2422,7 +2428,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2443,7 +2449,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2466,7 +2472,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2489,7 +2495,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2510,7 +2516,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2531,7 +2537,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -8664,7 +8670,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="7">
         <v>298</v>
       </c>
@@ -8685,7 +8691,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="7">
         <v>299</v>
       </c>
@@ -8706,7 +8712,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="7">
         <v>300</v>
       </c>
@@ -8727,7 +8733,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="7">
         <v>301</v>
       </c>
@@ -8748,7 +8754,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="7">
         <v>302</v>
       </c>
@@ -8769,7 +8775,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="7">
         <v>303</v>
       </c>
@@ -8790,588 +8796,588 @@
         <v>513</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D305" s="7">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E305" s="8">
-        <v>46040</v>
+        <v>45998</v>
       </c>
       <c r="F305" s="8"/>
       <c r="G305" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D306" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E306" s="8">
-        <v>45998</v>
+        <v>45978</v>
       </c>
       <c r="F306" s="8"/>
       <c r="G306" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D307" s="7">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E307" s="8">
-        <v>45978</v>
+        <v>45971</v>
       </c>
       <c r="F307" s="8"/>
       <c r="G307" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C308" s="7" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D308" s="7">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E308" s="8">
-        <v>45971</v>
+        <v>46010</v>
       </c>
       <c r="F308" s="8"/>
       <c r="G308" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D309" s="7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E309" s="8">
-        <v>46010</v>
+        <v>45999</v>
       </c>
       <c r="F309" s="8"/>
       <c r="G309" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D310" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E310" s="8">
-        <v>45999</v>
+        <v>46003</v>
       </c>
       <c r="F310" s="8"/>
       <c r="G310" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B311" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D311" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E311" s="8">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="F311" s="8"/>
       <c r="G311" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="D312" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E312" s="8">
-        <v>46006</v>
+        <v>46033</v>
       </c>
       <c r="F312" s="8"/>
       <c r="G312" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D313" s="7">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E313" s="8">
-        <v>46033</v>
+        <v>46027</v>
       </c>
       <c r="F313" s="8"/>
       <c r="G313" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D314" s="7">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E314" s="8">
-        <v>46033</v>
+        <v>45998</v>
       </c>
       <c r="F314" s="8"/>
       <c r="G314" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D315" s="7">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E315" s="8">
-        <v>46027</v>
+        <v>46058</v>
       </c>
       <c r="F315" s="8"/>
       <c r="G315" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D316" s="7">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E316" s="8">
-        <v>45998</v>
+        <v>46049</v>
       </c>
       <c r="F316" s="8"/>
       <c r="G316" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="D317" s="7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E317" s="8">
-        <v>46058</v>
+        <v>46019</v>
       </c>
       <c r="F317" s="8"/>
       <c r="G317" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="D318" s="7">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="E318" s="8">
-        <v>46049</v>
+        <v>46022</v>
       </c>
       <c r="F318" s="8"/>
       <c r="G318" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C319" s="7" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="D319" s="7">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E319" s="8">
-        <v>46019</v>
+        <v>46007</v>
       </c>
       <c r="F319" s="8"/>
       <c r="G319" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B320" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C320" s="7" t="s">
-        <v>314</v>
+        <v>347</v>
       </c>
       <c r="D320" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E320" s="8">
-        <v>46022</v>
+        <v>46023</v>
       </c>
       <c r="F320" s="8"/>
       <c r="G320" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>313</v>
+        <v>348</v>
       </c>
       <c r="C321" s="7" t="s">
         <v>314</v>
       </c>
       <c r="D321" s="7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E321" s="8">
-        <v>46006</v>
+        <v>46023</v>
       </c>
       <c r="F321" s="8"/>
       <c r="G321" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D322" s="7">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E322" s="8">
-        <v>46007</v>
+        <v>46058</v>
       </c>
       <c r="F322" s="8"/>
       <c r="G322" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D323" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E323" s="8">
-        <v>46023</v>
+        <v>46009</v>
       </c>
       <c r="F323" s="8"/>
       <c r="G323" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D324" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E324" s="8">
-        <v>46023</v>
+        <v>46019</v>
       </c>
       <c r="F324" s="8"/>
       <c r="G324" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D325" s="7">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E325" s="8">
-        <v>46058</v>
+        <v>46054</v>
       </c>
       <c r="F325" s="8"/>
       <c r="G325" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="D326" s="7">
         <v>13</v>
       </c>
       <c r="E326" s="8">
-        <v>46009</v>
+        <v>46015</v>
       </c>
       <c r="F326" s="8"/>
       <c r="G326" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="D327" s="7">
-        <v>23</v>
+        <v>1025</v>
       </c>
       <c r="E327" s="8">
-        <v>46019</v>
+        <v>45992</v>
       </c>
       <c r="F327" s="8"/>
       <c r="G327" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="D328" s="7">
-        <v>28</v>
+        <v>610</v>
       </c>
       <c r="E328" s="8">
-        <v>46054</v>
+        <v>45996</v>
       </c>
       <c r="F328" s="8"/>
       <c r="G328" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>323</v>
+        <v>360</v>
       </c>
       <c r="D329" s="7">
-        <v>13</v>
+        <v>651</v>
       </c>
       <c r="E329" s="8">
-        <v>46015</v>
+        <v>45991</v>
       </c>
       <c r="F329" s="8"/>
       <c r="G329" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B330" s="7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D330" s="7">
-        <v>1000</v>
+        <v>494</v>
       </c>
       <c r="E330" s="8">
-        <v>45992</v>
+        <v>46016</v>
       </c>
       <c r="F330" s="8"/>
       <c r="G330" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B331" s="7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D331" s="7">
-        <v>610</v>
+        <v>684</v>
       </c>
       <c r="E331" s="8">
-        <v>45996</v>
+        <v>46039</v>
       </c>
       <c r="F331" s="8"/>
       <c r="G331" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B332" s="7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D332" s="7">
-        <v>651</v>
+        <v>515</v>
       </c>
       <c r="E332" s="8">
-        <v>45991</v>
+        <v>46045</v>
       </c>
       <c r="F332" s="8"/>
       <c r="G332" s="7" t="s">
@@ -9380,114 +9386,30 @@
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C333" s="7" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D333" s="7">
-        <v>494</v>
+        <v>544</v>
       </c>
       <c r="E333" s="8">
-        <v>46016</v>
+        <v>46021</v>
       </c>
       <c r="F333" s="8"/>
       <c r="G333" s="7" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="7">
-        <v>333</v>
-      </c>
-      <c r="B334" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="C334" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D334" s="7">
-        <v>684</v>
-      </c>
-      <c r="E334" s="8">
-        <v>46039</v>
-      </c>
-      <c r="F334" s="8"/>
-      <c r="G334" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="7">
-        <v>334</v>
-      </c>
-      <c r="B335" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C335" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D335" s="7">
-        <v>515</v>
-      </c>
-      <c r="E335" s="8">
-        <v>46045</v>
-      </c>
-      <c r="F335" s="8"/>
-      <c r="G335" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="7">
-        <v>336</v>
-      </c>
-      <c r="B336" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C336" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D336" s="7">
-        <v>544</v>
-      </c>
-      <c r="E336" s="8">
-        <v>46021</v>
-      </c>
-      <c r="F336" s="8"/>
-      <c r="G336" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A337">
-        <v>337</v>
-      </c>
-      <c r="B337" t="s">
-        <v>356</v>
-      </c>
-      <c r="C337" t="s">
-        <v>566</v>
-      </c>
-      <c r="D337">
-        <v>1000</v>
-      </c>
-      <c r="E337" s="6">
-        <v>45992</v>
-      </c>
-      <c r="G337" t="s">
-        <v>513</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F337" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
-    <filterColumn colId="1">
+  <autoFilter ref="A1:K333" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
+    <filterColumn colId="6">
       <filters>
-        <filter val="RG80GS35153"/>
-        <filter val="RG80GS35153Y"/>
+        <filter val="WIP"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.DEV\TEST_python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD7E5DA-A0A4-4A8F-8418-7A51C9595AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B339C12-1B3C-421E-9310-4B5DA5A46E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{5B6232BF-90C2-4A8C-9297-D00C1332E89E}"/>
+    <workbookView xWindow="-19320" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{5B6232BF-90C2-4A8C-9297-D00C1332E89E}"/>
   </bookViews>
   <sheets>
     <sheet name="inventory" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">BOM!$A$1:$D$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">inventory!$A$1:$K$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2206,7 +2207,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G333"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8673,7 +8673,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="7">
         <v>298</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="7">
         <v>299</v>
       </c>
@@ -8715,7 +8715,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="7">
         <v>300</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="7">
         <v>301</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="7">
         <v>302</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="7">
         <v>303</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="7">
         <v>305</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="7">
         <v>306</v>
       </c>
@@ -8841,7 +8841,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="7">
         <v>307</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>323</v>
       </c>
       <c r="D307" s="7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E307" s="8">
         <v>45971</v>
@@ -8862,7 +8862,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="7">
         <v>308</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="7">
         <v>309</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="7">
         <v>310</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="7">
         <v>311</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A312" s="7">
         <v>312</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="7">
         <v>314</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="7">
         <v>315</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="7">
         <v>316</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="7">
         <v>317</v>
       </c>
@@ -9051,7 +9051,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="7">
         <v>318</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="7">
         <v>319</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="7">
         <v>321</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="7">
         <v>322</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="7">
         <v>323</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="7">
         <v>324</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="7">
         <v>325</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="7">
         <v>326</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="7">
         <v>327</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="7">
         <v>328</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="7">
         <v>329</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="7">
         <v>330</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="7">
         <v>331</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="7">
         <v>332</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="7">
         <v>333</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" s="7">
         <v>334</v>
       </c>
@@ -9387,7 +9387,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="7">
         <v>336</v>
       </c>
@@ -9410,11 +9410,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K333" xr:uid="{ABEF4CD1-A42A-4427-9209-78D332EE860E}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="RM"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G298">
       <sortCondition ref="F1:F333"/>
     </sortState>
@@ -9443,6 +9438,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E226A9B-C910-4DA2-85D7-A4EDAD1E88ED}">
   <dimension ref="A1:G298"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
@@ -15899,8 +15898,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{9E226A9B-C910-4DA2-85D7-A4EDAD1E88ED}"/>
   <conditionalFormatting sqref="B1:B298">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:B13">
     <cfRule type="colorScale" priority="2">
@@ -17945,7 +17945,7 @@
   </sheetData>
   <autoFilter ref="A1:D183" xr:uid="{3AB63DC0-C6F4-49B3-A9D9-717587D0D359}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
